--- a/воры/Amazing_Pics_SKU ALL_14.08.2026.xlsx
+++ b/воры/Amazing_Pics_SKU ALL_14.08.2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\воры\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4771137-1623-49E9-9F54-DC397360F95C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FECBB366-3AA0-4F5B-B16E-254BEFDE34A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7714,12 +7714,8 @@
       <c r="B229" s="13">
         <v>1912202740</v>
       </c>
-      <c r="C229" s="15">
-        <v>4860512678</v>
-      </c>
-      <c r="D229" s="15">
-        <v>3032683347</v>
-      </c>
+      <c r="C229" s="15"/>
+      <c r="D229" s="15"/>
       <c r="E229" s="15">
         <v>2914016450</v>
       </c>
@@ -9879,9 +9875,15 @@
       <c r="B306" s="13">
         <v>2474255592</v>
       </c>
-      <c r="C306" s="15"/>
-      <c r="D306" s="15"/>
-      <c r="E306" s="15"/>
+      <c r="C306" s="15">
+        <v>4860780531</v>
+      </c>
+      <c r="D306" s="15">
+        <v>5526393858</v>
+      </c>
+      <c r="E306" s="15">
+        <v>5639403861</v>
+      </c>
       <c r="F306" s="15"/>
       <c r="G306" s="15"/>
       <c r="H306" s="15"/>
@@ -9906,8 +9908,12 @@
       <c r="B307" s="13">
         <v>2474254273</v>
       </c>
-      <c r="C307" s="15"/>
-      <c r="D307" s="15"/>
+      <c r="C307" s="15">
+        <v>4860782393</v>
+      </c>
+      <c r="D307" s="15">
+        <v>5639404449</v>
+      </c>
       <c r="E307" s="15"/>
       <c r="F307" s="15"/>
       <c r="G307" s="15"/>
@@ -9933,8 +9939,12 @@
       <c r="B308" s="13">
         <v>2474251571</v>
       </c>
-      <c r="C308" s="15"/>
-      <c r="D308" s="15"/>
+      <c r="C308" s="15">
+        <v>4860777633</v>
+      </c>
+      <c r="D308" s="15">
+        <v>5639403331</v>
+      </c>
       <c r="E308" s="15"/>
       <c r="F308" s="15"/>
       <c r="G308" s="15"/>
@@ -10122,8 +10132,12 @@
       <c r="B315" s="13">
         <v>2474252891</v>
       </c>
-      <c r="C315" s="15"/>
-      <c r="D315" s="15"/>
+      <c r="C315" s="15">
+        <v>4860778560</v>
+      </c>
+      <c r="D315" s="15">
+        <v>5639403823</v>
+      </c>
       <c r="E315" s="15"/>
       <c r="F315" s="15"/>
       <c r="G315" s="15"/>

--- a/воры/Amazing_Pics_SKU ALL_14.08.2026.xlsx
+++ b/воры/Amazing_Pics_SKU ALL_14.08.2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\воры\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FECBB366-3AA0-4F5B-B16E-254BEFDE34A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB4BF1B7-9B58-49AC-96A5-45BA9C08407D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1812,8 +1812,12 @@
       <c r="B2" s="13">
         <v>1506380691</v>
       </c>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
+      <c r="C2" s="18">
+        <v>5523495879</v>
+      </c>
+      <c r="D2" s="18">
+        <v>5739114331</v>
+      </c>
       <c r="E2" s="18"/>
       <c r="F2" s="18"/>
       <c r="G2" s="18"/>
@@ -1838,9 +1842,15 @@
       <c r="B3" s="13">
         <v>1506320059</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
+      <c r="C3" s="15">
+        <v>4891860819</v>
+      </c>
+      <c r="D3" s="15">
+        <v>5628264284</v>
+      </c>
+      <c r="E3" s="15">
+        <v>5628265193</v>
+      </c>
       <c r="F3" s="15"/>
       <c r="G3" s="15"/>
       <c r="H3" s="15"/>
@@ -1864,8 +1874,12 @@
       <c r="B4" s="13">
         <v>1506318673</v>
       </c>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
+      <c r="C4" s="15">
+        <v>5523492294</v>
+      </c>
+      <c r="D4" s="15">
+        <v>5739111340</v>
+      </c>
       <c r="E4" s="15"/>
       <c r="F4" s="15"/>
       <c r="G4" s="15"/>
@@ -1890,7 +1904,9 @@
       <c r="B5" s="13">
         <v>1506381390</v>
       </c>
-      <c r="C5" s="15"/>
+      <c r="C5" s="15">
+        <v>5628262628</v>
+      </c>
       <c r="D5" s="15"/>
       <c r="E5" s="15"/>
       <c r="F5" s="15"/>
@@ -1916,7 +1932,9 @@
       <c r="B6" s="13">
         <v>1506318830</v>
       </c>
-      <c r="C6" s="15"/>
+      <c r="C6" s="15">
+        <v>4860842187</v>
+      </c>
       <c r="D6" s="15"/>
       <c r="E6" s="15"/>
       <c r="F6" s="15"/>
@@ -1942,7 +1960,9 @@
       <c r="B7" s="13">
         <v>1506332556</v>
       </c>
-      <c r="C7" s="15"/>
+      <c r="C7" s="15">
+        <v>5535142932</v>
+      </c>
       <c r="D7" s="15"/>
       <c r="E7" s="15"/>
       <c r="F7" s="15"/>
@@ -1968,7 +1988,9 @@
       <c r="B8" s="13">
         <v>1506318448</v>
       </c>
-      <c r="C8" s="15"/>
+      <c r="C8" s="15">
+        <v>4860838767</v>
+      </c>
       <c r="D8" s="15"/>
       <c r="E8" s="15"/>
       <c r="F8" s="15"/>
@@ -1994,7 +2016,9 @@
       <c r="B9" s="13">
         <v>1506319309</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="15">
+        <v>5739119077</v>
+      </c>
       <c r="D9" s="15"/>
       <c r="E9" s="15"/>
       <c r="F9" s="15"/>
@@ -2020,7 +2044,9 @@
       <c r="B10" s="13">
         <v>1506331021</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="15">
+        <v>5628265368</v>
+      </c>
       <c r="D10" s="15"/>
       <c r="E10" s="15"/>
       <c r="F10" s="15"/>
@@ -2046,7 +2072,9 @@
       <c r="B11" s="13">
         <v>1506318961</v>
       </c>
-      <c r="C11" s="15"/>
+      <c r="C11" s="15">
+        <v>5534845933</v>
+      </c>
       <c r="D11" s="15"/>
       <c r="E11" s="15"/>
       <c r="F11" s="15"/>
@@ -2072,7 +2100,9 @@
       <c r="B12" s="13">
         <v>1506318312</v>
       </c>
-      <c r="C12" s="15"/>
+      <c r="C12" s="15">
+        <v>5551386638</v>
+      </c>
       <c r="D12" s="15"/>
       <c r="E12" s="15"/>
       <c r="F12" s="15"/>
@@ -2098,7 +2128,9 @@
       <c r="B13" s="13">
         <v>1506318681</v>
       </c>
-      <c r="C13" s="16"/>
+      <c r="C13" s="16">
+        <v>5550845301</v>
+      </c>
       <c r="D13" s="15"/>
       <c r="E13" s="15"/>
       <c r="F13" s="15"/>
@@ -2124,7 +2156,9 @@
       <c r="B14" s="13">
         <v>1506319067</v>
       </c>
-      <c r="C14" s="15"/>
+      <c r="C14" s="15">
+        <v>5551235816</v>
+      </c>
       <c r="D14" s="15"/>
       <c r="E14" s="15"/>
       <c r="F14" s="15"/>
@@ -2150,7 +2184,9 @@
       <c r="B15" s="13">
         <v>1506319200</v>
       </c>
-      <c r="C15" s="15"/>
+      <c r="C15" s="15">
+        <v>5550879988</v>
+      </c>
       <c r="D15" s="15"/>
       <c r="E15" s="15"/>
       <c r="F15" s="15"/>
@@ -2176,7 +2212,9 @@
       <c r="B16" s="13">
         <v>1506333119</v>
       </c>
-      <c r="C16" s="16"/>
+      <c r="C16" s="16">
+        <v>5628263961</v>
+      </c>
       <c r="D16" s="15"/>
       <c r="E16" s="15"/>
       <c r="F16" s="15"/>
@@ -2202,8 +2240,12 @@
       <c r="B17" s="13">
         <v>1506319410</v>
       </c>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
+      <c r="C17" s="15">
+        <v>5739114735</v>
+      </c>
+      <c r="D17" s="15">
+        <v>5550905263</v>
+      </c>
       <c r="E17" s="15"/>
       <c r="F17" s="15"/>
       <c r="G17" s="15"/>
@@ -2228,7 +2270,9 @@
       <c r="B18" s="13">
         <v>1506318769</v>
       </c>
-      <c r="C18" s="15"/>
+      <c r="C18" s="15">
+        <v>5523477413</v>
+      </c>
       <c r="D18" s="15"/>
       <c r="E18" s="15"/>
       <c r="F18" s="15"/>
@@ -6700,9 +6744,15 @@
       <c r="B190" s="13">
         <v>1738653148</v>
       </c>
-      <c r="C190" s="15"/>
-      <c r="D190" s="15"/>
-      <c r="E190" s="15"/>
+      <c r="C190" s="15">
+        <v>4850072951</v>
+      </c>
+      <c r="D190" s="15">
+        <v>4860273508</v>
+      </c>
+      <c r="E190" s="15">
+        <v>4890108647</v>
+      </c>
       <c r="F190" s="15"/>
       <c r="G190" s="15"/>
       <c r="H190" s="15"/>
@@ -6726,9 +6776,15 @@
       <c r="B191" s="13">
         <v>1738652878</v>
       </c>
-      <c r="C191" s="15"/>
-      <c r="D191" s="15"/>
-      <c r="E191" s="15"/>
+      <c r="C191" s="15">
+        <v>4850069541</v>
+      </c>
+      <c r="D191" s="15">
+        <v>4850079851</v>
+      </c>
+      <c r="E191" s="15">
+        <v>4860278551</v>
+      </c>
       <c r="F191" s="15"/>
       <c r="G191" s="15"/>
       <c r="H191" s="15"/>
@@ -6752,11 +6808,21 @@
       <c r="B192" s="13">
         <v>1738651684</v>
       </c>
-      <c r="C192" s="15"/>
-      <c r="D192" s="15"/>
-      <c r="E192" s="15"/>
-      <c r="F192" s="15"/>
-      <c r="G192" s="15"/>
+      <c r="C192" s="15">
+        <v>4850067703</v>
+      </c>
+      <c r="D192" s="15">
+        <v>4850104406</v>
+      </c>
+      <c r="E192" s="15">
+        <v>4860268287</v>
+      </c>
+      <c r="F192" s="15">
+        <v>5020348020</v>
+      </c>
+      <c r="G192" s="15">
+        <v>5563970124</v>
+      </c>
       <c r="H192" s="15"/>
       <c r="I192" s="15"/>
       <c r="J192" s="15"/>
@@ -6778,8 +6844,12 @@
       <c r="B193" s="13">
         <v>1738651926</v>
       </c>
-      <c r="C193" s="15"/>
-      <c r="D193" s="15"/>
+      <c r="C193" s="15">
+        <v>5019833445</v>
+      </c>
+      <c r="D193" s="15">
+        <v>4850080678</v>
+      </c>
       <c r="E193" s="15"/>
       <c r="F193" s="15"/>
       <c r="G193" s="15"/>
@@ -6804,9 +6874,15 @@
       <c r="B194" s="13">
         <v>1738652063</v>
       </c>
-      <c r="C194" s="15"/>
-      <c r="D194" s="15"/>
-      <c r="E194" s="15"/>
+      <c r="C194" s="15">
+        <v>4850062261</v>
+      </c>
+      <c r="D194" s="15">
+        <v>4850068731</v>
+      </c>
+      <c r="E194" s="15">
+        <v>4890101076</v>
+      </c>
       <c r="F194" s="15"/>
       <c r="G194" s="15"/>
       <c r="H194" s="15"/>
@@ -6830,8 +6906,12 @@
       <c r="B195" s="13">
         <v>1738652367</v>
       </c>
-      <c r="C195" s="15"/>
-      <c r="D195" s="15"/>
+      <c r="C195" s="15">
+        <v>4890089349</v>
+      </c>
+      <c r="D195" s="15">
+        <v>4850064472</v>
+      </c>
       <c r="E195" s="15"/>
       <c r="F195" s="15"/>
       <c r="G195" s="15"/>
@@ -6934,8 +7014,12 @@
       <c r="B199" s="13">
         <v>1750746301</v>
       </c>
-      <c r="C199" s="15"/>
-      <c r="D199" s="15"/>
+      <c r="C199" s="15">
+        <v>4860835459</v>
+      </c>
+      <c r="D199" s="15">
+        <v>4860837012</v>
+      </c>
       <c r="E199" s="15"/>
       <c r="F199" s="15"/>
       <c r="G199" s="15"/>
@@ -6986,8 +7070,12 @@
       <c r="B201" s="13">
         <v>1750745576</v>
       </c>
-      <c r="C201" s="15"/>
-      <c r="D201" s="15"/>
+      <c r="C201" s="15">
+        <v>4860839299</v>
+      </c>
+      <c r="D201" s="15">
+        <v>4860840121</v>
+      </c>
       <c r="E201" s="15"/>
       <c r="F201" s="15"/>
       <c r="G201" s="15"/>
@@ -7012,8 +7100,12 @@
       <c r="B202" s="13">
         <v>1849771468</v>
       </c>
-      <c r="C202" s="15"/>
-      <c r="D202" s="15"/>
+      <c r="C202" s="15">
+        <v>4890089053</v>
+      </c>
+      <c r="D202" s="15">
+        <v>4850061910</v>
+      </c>
       <c r="E202" s="15"/>
       <c r="F202" s="15"/>
       <c r="G202" s="15"/>
@@ -7376,9 +7468,15 @@
       <c r="B216" s="13">
         <v>1849778023</v>
       </c>
-      <c r="C216" s="15"/>
-      <c r="D216" s="15"/>
-      <c r="E216" s="15"/>
+      <c r="C216" s="15">
+        <v>4850112766</v>
+      </c>
+      <c r="D216" s="15">
+        <v>4860265590</v>
+      </c>
+      <c r="E216" s="15">
+        <v>4890090671</v>
+      </c>
       <c r="F216" s="15"/>
       <c r="G216" s="15"/>
       <c r="H216" s="15"/>
@@ -7402,8 +7500,12 @@
       <c r="B217" s="13">
         <v>1849777600</v>
       </c>
-      <c r="C217" s="15"/>
-      <c r="D217" s="15"/>
+      <c r="C217" s="15">
+        <v>4890087776</v>
+      </c>
+      <c r="D217" s="15">
+        <v>4850054918</v>
+      </c>
       <c r="E217" s="15"/>
       <c r="F217" s="15"/>
       <c r="G217" s="15"/>
@@ -7716,9 +7818,7 @@
       </c>
       <c r="C229" s="15"/>
       <c r="D229" s="15"/>
-      <c r="E229" s="15">
-        <v>2914016450</v>
-      </c>
+      <c r="E229" s="15"/>
       <c r="F229" s="15"/>
       <c r="G229" s="15"/>
       <c r="H229" s="15"/>
@@ -7742,9 +7842,7 @@
       <c r="B230" s="13">
         <v>1912202107</v>
       </c>
-      <c r="C230" s="15">
-        <v>4860510892</v>
-      </c>
+      <c r="C230" s="15"/>
       <c r="D230" s="15"/>
       <c r="E230" s="15"/>
       <c r="F230" s="15"/>
@@ -7770,9 +7868,7 @@
       <c r="B231" s="13">
         <v>1912202149</v>
       </c>
-      <c r="C231" s="15">
-        <v>4860512387</v>
-      </c>
+      <c r="C231" s="15"/>
       <c r="D231" s="15"/>
       <c r="E231" s="15"/>
       <c r="F231" s="15"/>
@@ -7798,9 +7894,7 @@
       <c r="B232" s="13">
         <v>1912201742</v>
       </c>
-      <c r="C232" s="15">
-        <v>4860515739</v>
-      </c>
+      <c r="C232" s="15"/>
       <c r="D232" s="15"/>
       <c r="E232" s="15"/>
       <c r="F232" s="15"/>
@@ -7826,9 +7920,7 @@
       <c r="B233" s="13">
         <v>1912202033</v>
       </c>
-      <c r="C233" s="15">
-        <v>4860515314</v>
-      </c>
+      <c r="C233" s="15"/>
       <c r="D233" s="15"/>
       <c r="E233" s="15"/>
       <c r="F233" s="15"/>
@@ -7854,12 +7946,8 @@
       <c r="B234" s="13">
         <v>1912202814</v>
       </c>
-      <c r="C234" s="15">
-        <v>4860514981</v>
-      </c>
-      <c r="D234" s="15">
-        <v>2914040507</v>
-      </c>
+      <c r="C234" s="15"/>
+      <c r="D234" s="15"/>
       <c r="E234" s="15"/>
       <c r="F234" s="15"/>
       <c r="G234" s="15"/>
@@ -7884,9 +7972,7 @@
       <c r="B235" s="13">
         <v>1912202105</v>
       </c>
-      <c r="C235" s="15">
-        <v>4860514936</v>
-      </c>
+      <c r="C235" s="15"/>
       <c r="D235" s="15"/>
       <c r="E235" s="15"/>
       <c r="F235" s="15"/>
@@ -7912,9 +7998,7 @@
       <c r="B236" s="13">
         <v>1912202818</v>
       </c>
-      <c r="C236" s="15">
-        <v>4860516268</v>
-      </c>
+      <c r="C236" s="15"/>
       <c r="D236" s="15"/>
       <c r="E236" s="15"/>
       <c r="F236" s="15"/>
@@ -7940,9 +8024,7 @@
       <c r="B237" s="13">
         <v>1912202795</v>
       </c>
-      <c r="C237" s="15">
-        <v>4860515804</v>
-      </c>
+      <c r="C237" s="15"/>
       <c r="D237" s="15"/>
       <c r="E237" s="15"/>
       <c r="F237" s="15"/>
@@ -7968,9 +8050,7 @@
       <c r="B238" s="13">
         <v>1912202099</v>
       </c>
-      <c r="C238" s="15">
-        <v>4860515117</v>
-      </c>
+      <c r="C238" s="15"/>
       <c r="D238" s="15"/>
       <c r="E238" s="15"/>
       <c r="F238" s="15"/>
@@ -7996,9 +8076,7 @@
       <c r="B239" s="13">
         <v>1912202725</v>
       </c>
-      <c r="C239" s="15">
-        <v>4860514830</v>
-      </c>
+      <c r="C239" s="15"/>
       <c r="D239" s="15"/>
       <c r="E239" s="15"/>
       <c r="F239" s="15"/>
@@ -8024,12 +8102,8 @@
       <c r="B240" s="13">
         <v>1912202762</v>
       </c>
-      <c r="C240" s="15">
-        <v>4860510682</v>
-      </c>
-      <c r="D240" s="15">
-        <v>5260115221</v>
-      </c>
+      <c r="C240" s="15"/>
+      <c r="D240" s="15"/>
       <c r="E240" s="15"/>
       <c r="F240" s="15"/>
       <c r="G240" s="15"/>
@@ -8584,15 +8658,9 @@
       <c r="B261" s="13">
         <v>2449979383</v>
       </c>
-      <c r="C261" s="16">
-        <v>4927493807</v>
-      </c>
-      <c r="D261" s="15">
-        <v>4927493771</v>
-      </c>
-      <c r="E261" s="15">
-        <v>4850285859</v>
-      </c>
+      <c r="C261" s="16"/>
+      <c r="D261" s="15"/>
+      <c r="E261" s="15"/>
       <c r="F261" s="15"/>
       <c r="G261" s="15"/>
       <c r="H261" s="15"/>
@@ -8617,18 +8685,10 @@
       <c r="B262" s="13">
         <v>2449977151</v>
       </c>
-      <c r="C262" s="15">
-        <v>4927493944</v>
-      </c>
-      <c r="D262" s="15">
-        <v>4927492360</v>
-      </c>
-      <c r="E262" s="15">
-        <v>4850257674</v>
-      </c>
-      <c r="F262" s="15">
-        <v>4850283623</v>
-      </c>
+      <c r="C262" s="15"/>
+      <c r="D262" s="15"/>
+      <c r="E262" s="15"/>
+      <c r="F262" s="15"/>
       <c r="G262" s="15"/>
       <c r="H262" s="15"/>
       <c r="I262" s="15"/>
@@ -8652,15 +8712,9 @@
       <c r="B263" s="13">
         <v>2449977812</v>
       </c>
-      <c r="C263" s="16">
-        <v>4927494204</v>
-      </c>
-      <c r="D263" s="15">
-        <v>5051075670</v>
-      </c>
-      <c r="E263" s="15">
-        <v>4927495093</v>
-      </c>
+      <c r="C263" s="16"/>
+      <c r="D263" s="15"/>
+      <c r="E263" s="15"/>
       <c r="F263" s="15"/>
       <c r="G263" s="15"/>
       <c r="H263" s="15"/>
@@ -8685,18 +8739,10 @@
       <c r="B264" s="13">
         <v>2449977848</v>
       </c>
-      <c r="C264" s="15">
-        <v>4927492876</v>
-      </c>
-      <c r="D264" s="15">
-        <v>4927492142</v>
-      </c>
-      <c r="E264" s="15">
-        <v>5051047094</v>
-      </c>
-      <c r="F264" s="15">
-        <v>4927493274</v>
-      </c>
+      <c r="C264" s="15"/>
+      <c r="D264" s="15"/>
+      <c r="E264" s="15"/>
+      <c r="F264" s="15"/>
       <c r="G264" s="15"/>
       <c r="H264" s="15"/>
       <c r="I264" s="15"/>
@@ -8720,15 +8766,9 @@
       <c r="B265" s="13">
         <v>2449977623</v>
       </c>
-      <c r="C265" s="15">
-        <v>4927492788</v>
-      </c>
-      <c r="D265" s="15">
-        <v>4927493773</v>
-      </c>
-      <c r="E265" s="15">
-        <v>4927492788</v>
-      </c>
+      <c r="C265" s="15"/>
+      <c r="D265" s="15"/>
+      <c r="E265" s="15"/>
       <c r="F265" s="15"/>
       <c r="G265" s="15"/>
       <c r="H265" s="15"/>
@@ -8753,15 +8793,9 @@
       <c r="B266" s="13">
         <v>2449976760</v>
       </c>
-      <c r="C266" s="15">
-        <v>4927491618</v>
-      </c>
-      <c r="D266" s="15">
-        <v>4927493012</v>
-      </c>
-      <c r="E266" s="15">
-        <v>4850263592</v>
-      </c>
+      <c r="C266" s="15"/>
+      <c r="D266" s="15"/>
+      <c r="E266" s="15"/>
       <c r="F266" s="15"/>
       <c r="G266" s="15"/>
       <c r="H266" s="15"/>
@@ -8786,15 +8820,9 @@
       <c r="B267" s="13">
         <v>2449978556</v>
       </c>
-      <c r="C267" s="15">
-        <v>4927492315</v>
-      </c>
-      <c r="D267" s="15">
-        <v>4927494185</v>
-      </c>
-      <c r="E267" s="15">
-        <v>5051070714</v>
-      </c>
+      <c r="C267" s="15"/>
+      <c r="D267" s="15"/>
+      <c r="E267" s="15"/>
       <c r="F267" s="15"/>
       <c r="G267" s="15"/>
       <c r="H267" s="15"/>
@@ -8819,15 +8847,9 @@
       <c r="B268" s="13">
         <v>2449976743</v>
       </c>
-      <c r="C268" s="15">
-        <v>4927491817</v>
-      </c>
-      <c r="D268" s="15">
-        <v>5051055610</v>
-      </c>
-      <c r="E268" s="15">
-        <v>5051053039</v>
-      </c>
+      <c r="C268" s="15"/>
+      <c r="D268" s="15"/>
+      <c r="E268" s="15"/>
       <c r="F268" s="15"/>
       <c r="G268" s="15"/>
       <c r="H268" s="15"/>
@@ -8852,18 +8874,10 @@
       <c r="B269" s="13">
         <v>2449977121</v>
       </c>
-      <c r="C269" s="15">
-        <v>4927493897</v>
-      </c>
-      <c r="D269" s="15">
-        <v>4927492219</v>
-      </c>
-      <c r="E269" s="15">
-        <v>4850273569</v>
-      </c>
-      <c r="F269" s="15">
-        <v>4850273569</v>
-      </c>
+      <c r="C269" s="15"/>
+      <c r="D269" s="15"/>
+      <c r="E269" s="15"/>
+      <c r="F269" s="15"/>
       <c r="G269" s="15"/>
       <c r="H269" s="15"/>
       <c r="I269" s="15"/>
@@ -8887,18 +8901,10 @@
       <c r="B270" s="13">
         <v>2449976996</v>
       </c>
-      <c r="C270" s="15">
-        <v>4927495300</v>
-      </c>
-      <c r="D270" s="15">
-        <v>4927493310</v>
-      </c>
-      <c r="E270" s="15">
-        <v>4850250748</v>
-      </c>
-      <c r="F270" s="15">
-        <v>4850247314</v>
-      </c>
+      <c r="C270" s="15"/>
+      <c r="D270" s="15"/>
+      <c r="E270" s="15"/>
+      <c r="F270" s="15"/>
       <c r="G270" s="15"/>
       <c r="H270" s="15"/>
       <c r="I270" s="15"/>
@@ -8922,18 +8928,10 @@
       <c r="B271" s="13">
         <v>2449976986</v>
       </c>
-      <c r="C271" s="15">
-        <v>4927491780</v>
-      </c>
-      <c r="D271" s="15">
-        <v>5151924802</v>
-      </c>
-      <c r="E271" s="15">
-        <v>5151924802</v>
-      </c>
-      <c r="F271" s="15">
-        <v>4850262972</v>
-      </c>
+      <c r="C271" s="15"/>
+      <c r="D271" s="15"/>
+      <c r="E271" s="15"/>
+      <c r="F271" s="15"/>
       <c r="G271" s="15"/>
       <c r="H271" s="15"/>
       <c r="I271" s="15"/>
@@ -9875,15 +9873,9 @@
       <c r="B306" s="13">
         <v>2474255592</v>
       </c>
-      <c r="C306" s="15">
-        <v>4860780531</v>
-      </c>
-      <c r="D306" s="15">
-        <v>5526393858</v>
-      </c>
-      <c r="E306" s="15">
-        <v>5639403861</v>
-      </c>
+      <c r="C306" s="15"/>
+      <c r="D306" s="15"/>
+      <c r="E306" s="15"/>
       <c r="F306" s="15"/>
       <c r="G306" s="15"/>
       <c r="H306" s="15"/>
@@ -9908,12 +9900,8 @@
       <c r="B307" s="13">
         <v>2474254273</v>
       </c>
-      <c r="C307" s="15">
-        <v>4860782393</v>
-      </c>
-      <c r="D307" s="15">
-        <v>5639404449</v>
-      </c>
+      <c r="C307" s="15"/>
+      <c r="D307" s="15"/>
       <c r="E307" s="15"/>
       <c r="F307" s="15"/>
       <c r="G307" s="15"/>
@@ -9939,12 +9927,8 @@
       <c r="B308" s="13">
         <v>2474251571</v>
       </c>
-      <c r="C308" s="15">
-        <v>4860777633</v>
-      </c>
-      <c r="D308" s="15">
-        <v>5639403331</v>
-      </c>
+      <c r="C308" s="15"/>
+      <c r="D308" s="15"/>
       <c r="E308" s="15"/>
       <c r="F308" s="15"/>
       <c r="G308" s="15"/>
@@ -10132,12 +10116,8 @@
       <c r="B315" s="13">
         <v>2474252891</v>
       </c>
-      <c r="C315" s="15">
-        <v>4860778560</v>
-      </c>
-      <c r="D315" s="15">
-        <v>5639403823</v>
-      </c>
+      <c r="C315" s="15"/>
+      <c r="D315" s="15"/>
       <c r="E315" s="15"/>
       <c r="F315" s="15"/>
       <c r="G315" s="15"/>
@@ -11297,18 +11277,10 @@
       <c r="B358" s="13">
         <v>3697386517</v>
       </c>
-      <c r="C358" s="15">
-        <v>5152539218</v>
-      </c>
-      <c r="D358" s="15">
-        <v>4860343748</v>
-      </c>
-      <c r="E358" s="15">
-        <v>4860344231</v>
-      </c>
-      <c r="F358" s="15">
-        <v>5152540211</v>
-      </c>
+      <c r="C358" s="15"/>
+      <c r="D358" s="15"/>
+      <c r="E358" s="15"/>
+      <c r="F358" s="15"/>
       <c r="G358" s="15"/>
       <c r="H358" s="15"/>
       <c r="I358" s="15"/>
@@ -11359,15 +11331,9 @@
       <c r="B360" s="13">
         <v>3697386057</v>
       </c>
-      <c r="C360" s="15">
-        <v>4860340541</v>
-      </c>
-      <c r="D360" s="15">
-        <v>5152630417</v>
-      </c>
-      <c r="E360" s="15">
-        <v>5152544753</v>
-      </c>
+      <c r="C360" s="15"/>
+      <c r="D360" s="15"/>
+      <c r="E360" s="15"/>
       <c r="F360" s="15"/>
       <c r="G360" s="15"/>
       <c r="H360" s="15"/>
@@ -11392,18 +11358,10 @@
       <c r="B361" s="13">
         <v>3697386822</v>
       </c>
-      <c r="C361" s="15">
-        <v>5152675332</v>
-      </c>
-      <c r="D361" s="15">
-        <v>5151963646</v>
-      </c>
-      <c r="E361" s="15">
-        <v>4860349636</v>
-      </c>
-      <c r="F361" s="15">
-        <v>4964034624</v>
-      </c>
+      <c r="C361" s="15"/>
+      <c r="D361" s="15"/>
+      <c r="E361" s="15"/>
+      <c r="F361" s="15"/>
       <c r="G361" s="15"/>
       <c r="H361" s="15"/>
       <c r="I361" s="15"/>
@@ -11427,18 +11385,10 @@
       <c r="B362" s="13">
         <v>3697386529</v>
       </c>
-      <c r="C362" s="15">
-        <v>5152549435</v>
-      </c>
-      <c r="D362" s="15">
-        <v>4860346232</v>
-      </c>
-      <c r="E362" s="15">
-        <v>4860347247</v>
-      </c>
-      <c r="F362" s="15">
-        <v>4964037439</v>
-      </c>
+      <c r="C362" s="15"/>
+      <c r="D362" s="15"/>
+      <c r="E362" s="15"/>
+      <c r="F362" s="15"/>
       <c r="G362" s="15"/>
       <c r="H362" s="15"/>
       <c r="I362" s="15"/>
@@ -11813,24 +11763,12 @@
       <c r="B376" s="13">
         <v>3697504349</v>
       </c>
-      <c r="C376" s="16">
-        <v>4860339001</v>
-      </c>
-      <c r="D376" s="15">
-        <v>4860340285</v>
-      </c>
-      <c r="E376" s="15">
-        <v>4964032457</v>
-      </c>
-      <c r="F376" s="15">
-        <v>4860339126</v>
-      </c>
-      <c r="G376" s="15">
-        <v>5152644823</v>
-      </c>
-      <c r="H376" s="15">
-        <v>4802499342</v>
-      </c>
+      <c r="C376" s="16"/>
+      <c r="D376" s="15"/>
+      <c r="E376" s="15"/>
+      <c r="F376" s="15"/>
+      <c r="G376" s="15"/>
+      <c r="H376" s="15"/>
       <c r="I376" s="15"/>
       <c r="J376" s="15"/>
       <c r="K376" s="15"/>
@@ -12257,18 +12195,10 @@
       <c r="B392" s="13">
         <v>3697505659</v>
       </c>
-      <c r="C392" s="15">
-        <v>4860341677</v>
-      </c>
-      <c r="D392" s="15">
-        <v>4860343902</v>
-      </c>
-      <c r="E392" s="15">
-        <v>5152540352</v>
-      </c>
-      <c r="F392" s="15">
-        <v>5152619942</v>
-      </c>
+      <c r="C392" s="15"/>
+      <c r="D392" s="15"/>
+      <c r="E392" s="15"/>
+      <c r="F392" s="15"/>
       <c r="G392" s="15"/>
       <c r="H392" s="15"/>
       <c r="I392" s="15"/>
@@ -12292,15 +12222,9 @@
       <c r="B393" s="13">
         <v>3697504347</v>
       </c>
-      <c r="C393" s="15">
-        <v>4964035026</v>
-      </c>
-      <c r="D393" s="15">
-        <v>4860346226</v>
-      </c>
-      <c r="E393" s="15">
-        <v>5152622978</v>
-      </c>
+      <c r="C393" s="15"/>
+      <c r="D393" s="15"/>
+      <c r="E393" s="15"/>
       <c r="F393" s="15"/>
       <c r="G393" s="15"/>
       <c r="H393" s="15"/>
@@ -12325,21 +12249,11 @@
       <c r="B394" s="13">
         <v>3697504996</v>
       </c>
-      <c r="C394" s="15">
-        <v>4860354817</v>
-      </c>
-      <c r="D394" s="15">
-        <v>4860354817</v>
-      </c>
-      <c r="E394" s="15">
-        <v>5152533289</v>
-      </c>
-      <c r="F394" s="15">
-        <v>5152538336</v>
-      </c>
-      <c r="G394" s="15">
-        <v>5259847119</v>
-      </c>
+      <c r="C394" s="15"/>
+      <c r="D394" s="15"/>
+      <c r="E394" s="15"/>
+      <c r="F394" s="15"/>
+      <c r="G394" s="15"/>
       <c r="H394" s="15"/>
       <c r="I394" s="15"/>
       <c r="J394" s="15"/>
@@ -12362,15 +12276,9 @@
       <c r="B395" s="13">
         <v>3697504363</v>
       </c>
-      <c r="C395" s="16">
-        <v>4860351934</v>
-      </c>
-      <c r="D395" s="15">
-        <v>4964035879</v>
-      </c>
-      <c r="E395" s="15">
-        <v>4860347173</v>
-      </c>
+      <c r="C395" s="16"/>
+      <c r="D395" s="15"/>
+      <c r="E395" s="15"/>
       <c r="F395" s="15"/>
       <c r="G395" s="15"/>
       <c r="H395" s="15"/>
@@ -12395,18 +12303,10 @@
       <c r="B396" s="13">
         <v>3697505978</v>
       </c>
-      <c r="C396" s="15">
-        <v>4860337944</v>
-      </c>
-      <c r="D396" s="15">
-        <v>4860340874</v>
-      </c>
-      <c r="E396" s="15">
-        <v>4964034510</v>
-      </c>
-      <c r="F396" s="15">
-        <v>5152598411</v>
-      </c>
+      <c r="C396" s="15"/>
+      <c r="D396" s="15"/>
+      <c r="E396" s="15"/>
+      <c r="F396" s="15"/>
       <c r="G396" s="15"/>
       <c r="H396" s="15"/>
       <c r="I396" s="15"/>
@@ -12430,18 +12330,10 @@
       <c r="B397" s="13">
         <v>3697504998</v>
       </c>
-      <c r="C397" s="15">
-        <v>4860338833</v>
-      </c>
-      <c r="D397" s="15">
-        <v>4860340604</v>
-      </c>
-      <c r="E397" s="15">
-        <v>4964034517</v>
-      </c>
-      <c r="F397" s="15">
-        <v>4860338116</v>
-      </c>
+      <c r="C397" s="15"/>
+      <c r="D397" s="15"/>
+      <c r="E397" s="15"/>
+      <c r="F397" s="15"/>
       <c r="G397" s="15"/>
       <c r="H397" s="15"/>
       <c r="I397" s="15"/>
@@ -12465,18 +12357,10 @@
       <c r="B398" s="13">
         <v>3697504814</v>
       </c>
-      <c r="C398" s="15">
-        <v>5152601206</v>
-      </c>
-      <c r="D398" s="15">
-        <v>4860336076</v>
-      </c>
-      <c r="E398" s="15">
-        <v>4860337341</v>
-      </c>
-      <c r="F398" s="15">
-        <v>4964035282</v>
-      </c>
+      <c r="C398" s="15"/>
+      <c r="D398" s="15"/>
+      <c r="E398" s="15"/>
+      <c r="F398" s="15"/>
       <c r="G398" s="15"/>
       <c r="H398" s="15"/>
       <c r="I398" s="15"/>
@@ -12500,18 +12384,10 @@
       <c r="B399" s="13">
         <v>3697505764</v>
       </c>
-      <c r="C399" s="15">
-        <v>5152647883</v>
-      </c>
-      <c r="D399" s="15">
-        <v>4860340796</v>
-      </c>
-      <c r="E399" s="15">
-        <v>4860340796</v>
-      </c>
-      <c r="F399" s="15">
-        <v>4964038139</v>
-      </c>
+      <c r="C399" s="15"/>
+      <c r="D399" s="15"/>
+      <c r="E399" s="15"/>
+      <c r="F399" s="15"/>
       <c r="G399" s="15"/>
       <c r="H399" s="15"/>
       <c r="I399" s="15"/>
@@ -12535,18 +12411,10 @@
       <c r="B400" s="13">
         <v>3697506004</v>
       </c>
-      <c r="C400" s="15">
-        <v>5152537405</v>
-      </c>
-      <c r="D400" s="15">
-        <v>4860338207</v>
-      </c>
-      <c r="E400" s="15">
-        <v>4860367668</v>
-      </c>
-      <c r="F400" s="15">
-        <v>4964033197</v>
-      </c>
+      <c r="C400" s="15"/>
+      <c r="D400" s="15"/>
+      <c r="E400" s="15"/>
+      <c r="F400" s="15"/>
       <c r="G400" s="15"/>
       <c r="H400" s="15"/>
       <c r="I400" s="15"/>
@@ -12570,12 +12438,8 @@
       <c r="B401" s="13">
         <v>3697505436</v>
       </c>
-      <c r="C401" s="15">
-        <v>5152600265</v>
-      </c>
-      <c r="D401" s="15">
-        <v>4860336920</v>
-      </c>
+      <c r="C401" s="15"/>
+      <c r="D401" s="15"/>
       <c r="E401" s="15">
         <v>4860340587</v>
       </c>
